--- a/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>內分泌腺分泌的物質是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>內分泌</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>慢但持久</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>激素</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>代謝變慢</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>荷爾蒙</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>激素經什麼運送？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>代謝</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>血液</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>運送</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>調節血糖的激素來自？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>慢但持久</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>胰島</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>胰臟</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>緊張時分泌的激素來自？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>腎上腺</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>代謝</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>應急</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>內分泌作用較神經？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>腦下腺</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>降低血糖</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>慢但持久</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>緩慢</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>激素需要量多還少？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>微量即有效</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>被分解代謝</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>內分泌</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>少量</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>與神經共同協調的是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>內分泌</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>被分解代謝</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>兩系統</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>分泌生長激素的是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>腦下腺</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>代謝變慢</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>生長</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>胰島素由哪個器官分泌？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>胰臟(胰島)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>胰臟</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>內分泌訊息傳遞比神經？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>內分泌</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>慢但持久</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>被分解代謝</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>持久</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>激素為何能作用全身？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>心跳呼吸加速供能應急</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>神經快速短暫、內分泌緩慢持久,互補協調全身</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>隨血液到達各處</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>血液</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>胰島素的作用是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>胰島</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>降低血糖</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>腎上腺素使身體？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>進入應急狀態</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>心跳加速</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>甲狀腺激素影響？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>腦下腺</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>代謝率</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>神經與內分泌差別？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>性激素等促進生長與性徵發育</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>快短暫vs慢持久</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>內分泌調節的特點？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>疾病</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>血液</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>緩慢而持久</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>代謝變慢</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>持久</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>激素分泌失調可能導致？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>胰島</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>緩慢而持久</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>內分泌</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>疾病</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>失衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>內分泌不需導管直接分泌到？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>血液</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>慢但持久</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>進入應急狀態</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>被分解代謝</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>無導管</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>甲狀腺激素分泌不足可能影響？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>腎上腺</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>腦下腺</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>代謝變慢</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>微量即有效</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>激素作用完後通常會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>代謝變慢</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>激素</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>胰島</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>被分解代謝</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>代謝</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物4-2 內分泌與協調　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>比較神經與內分泌協調的差異與互補？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>具高度作用性針對特定目標</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>神經即時反應內分泌長期調節</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>神經快速短暫、內分泌緩慢持久,互補協調全身</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>互補</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>說明血糖過高時胰島素如何調節？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>如甲狀腺失調影響代謝</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>心跳呼吸加速供能應急</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>胰島素促使血糖被利用儲存使血糖下降</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何激素微量即能產生明顯效果？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>具高度作用性針對特定目標</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>效力</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>緊張時腎上腺素的生理作用？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>隨血液到達各處</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>心跳呼吸加速供能應急</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>性激素等促進生長與性徵發育</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>應急</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>內分泌失調對健康的影響舉例？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>如甲狀腺失調影響代謝</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>失調</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>神經與內分泌如何共同維持協調？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>神經即時反應內分泌長期調節</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>性激素等促進生長與性徵發育</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>如甲狀腺失調影響代謝</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>協調</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>激素隨血液運送的優缺點？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>可達全身但作用較慢</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>具高度作用性針對特定目標</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>青春期發育與激素的關係？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>性激素等促進生長與性徵發育</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>如甲狀腺失調影響代謝</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>神經快速短暫、內分泌緩慢持久,互補協調全身</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>發育</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>糖尿病與胰島素的關係？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>激素持久神經快速短暫</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>胰島素不足或失效使血糖過高</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>神經快速短暫、內分泌緩慢持久,互補協調全身</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>血糖</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何內分泌適合長期調節神經適合即時？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>激素持久神經快速短暫</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>快短暫vs慢持久</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>胰島素不足或失效使血糖過高</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>心跳呼吸加速供能應急</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>互補</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>荷爾蒙</t>
+          <t>荷爾蒙：內分泌腺分泌的物質稱為激素，也就是俗稱的荷爾蒙，能調節身體生理活動</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>運送</t>
+          <t>運送：激素分泌後會進入血液，隨血液循環運送到身體各部位發揮作用</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>胰臟</t>
+          <t>胰臟：調節血糖濃度的胰島素是由胰臟中的胰島所分泌</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>應急</t>
+          <t>應急：緊張或遇到危險時，腎上腺會分泌腎上腺素，讓身體進入應急狀態</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>緩慢</t>
+          <t>緩慢：內分泌系統的作用速度比神經系統慢，但效果維持得比較久</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>少量</t>
+          <t>少量：激素只要微量就能對身體產生明顯的調節作用，不需要大量分泌</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>兩系統</t>
+          <t>兩系統：內分泌系統會和神經系統一起合作，共同協調身體的生理活動</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>生長</t>
+          <t>生長：腦下腺會分泌生長激素，促進身體的生長發育</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>胰臟</t>
+          <t>胰臟：胰島素是由胰臟中的胰島細胞所分泌，用來調節血糖濃度</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>持久</t>
+          <t>持久：內分泌系統靠激素隨血液運送訊息，傳遞速度比神經慢，但作用效果通常比較持久</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>血液</t>
+          <t>血液：激素分泌後進入血液，能隨血液循環到達身體各個角落發揮作用</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：胰島素的作用是幫助細胞利用血液中的葡萄糖，使血糖濃度下降</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>心跳加速</t>
+          <t>心跳加速：腎上腺素會讓心跳和呼吸加快、供應更多能量，進入應急備戰狀態</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>代謝率</t>
+          <t>代謝率：甲狀腺分泌的甲狀腺激素會影響身體的新陳代謝速率</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：神經傳遞訊息快速但短暫，內分泌則作用較慢但效果持久，兩者互補</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>持久</t>
+          <t>持久：內分泌系統分泌的激素作用速度較慢，但效果能維持比較長的時間</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>失衡</t>
+          <t>失衡：激素分泌過多或過少都可能造成身體失調，進而引發疾病</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>無導管</t>
+          <t>無導管：內分泌腺沒有導管，會直接把激素分泌到血液中運送到全身</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>代謝</t>
+          <t>代謝：甲狀腺激素能促進身體的新陳代謝，分泌不足會使代謝速率變慢，容易感到疲倦、怕冷</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>代謝</t>
+          <t>代謝：激素完成調節作用後，通常會被身體分解代謝掉，避免持續作用影響身體平衡</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>互補</t>
+          <t>互補：神經快速短暫、內分泌緩慢持久，兩者互補合作共同協調全身</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：血糖過高時胰臟分泌胰島素，促使細胞吸收利用葡萄糖，血糖濃度隨之下降</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>效力</t>
+          <t>效力：激素具有很強的作用力，能精準作用在特定目標細胞上，微量就有明顯效果</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>應急</t>
+          <t>應急：緊張時腎上腺分泌腎上腺素，讓心跳呼吸加快，提供身體能量應付緊急狀況</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>失調</t>
+          <t>失調：例如甲狀腺激素分泌失調，會影響身體的新陳代謝速率，造成健康問題</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>協調</t>
+          <t>協調：神經系統負責即時快速的反應，內分泌系統負責長期持續的生理調節</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：激素隨血液運送能到達身體各處發揮作用，但相對神經傳遞來說速度較慢</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>發育</t>
+          <t>發育：青春期時性激素等激素分泌增加，會促進身體生長並使第二性徵發育</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>血糖</t>
+          <t>血糖：糖尿病患者體內胰島素分泌不足，或身體細胞對胰島素反應不佳，導致血糖無法被有效調節，長期偏高</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>為何內分泌適合長期調節神經適合即時？</t>
+          <t>為何內分泌適合長期調節、神經適合即時反應？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>快短暫vs慢持久</t>
+          <t>隨血液到達各處</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>胰島素不足或失效使血糖過高</t>
+          <t>胰島素促使血糖被利用儲存使血糖下降</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>心跳呼吸加速供能應急</t>
+          <t>如甲狀腺失調影響代謝</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>互補</t>
+          <t>互補：神經系統用電訊號傳遞，反應快但作用短暫，適合處理緊急、即時的狀況;內分泌系統靠激素隨血液運送，作用較慢但效果持久，適合處理需要長時間維持的生理調節，兩者互相搭配</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物4-2_三種難度測驗卷.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>微量即有效</t>
+          <t>內分泌</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>激素</t>
+          <t>緩慢而持久</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>激素</t>
+          <t>緩慢而持久</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>腎上腺</t>
+          <t>腦下腺</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>疾病</t>
+          <t>慢但持久</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>腦下腺</t>
+          <t>激素</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>腎上腺</t>
+          <t>疾病</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>腦下腺</t>
+          <t>慢但持久</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>微量即有效</t>
+          <t>胰臟(胰島)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>代謝變慢</t>
+          <t>內分泌</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>激素</t>
+          <t>腦下腺</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>胰島</t>
+          <t>血液</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
